--- a/research/traditional_assets/database/data/italy/italy_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.022995</v>
+        <v>0.07089999999999999</v>
       </c>
       <c r="E2">
-        <v>0.535</v>
+        <v>0.156</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.004907518516985972</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.004882691273223817</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.002131005089584971</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.001722946570393526</v>
       </c>
       <c r="K2">
-        <v>36.44</v>
+        <v>41.511</v>
       </c>
       <c r="L2">
-        <v>0.149344262295082</v>
+        <v>0.1717672859684694</v>
       </c>
       <c r="M2">
-        <v>25.5099</v>
+        <v>55.3172</v>
       </c>
       <c r="N2">
-        <v>0.06284774575018479</v>
+        <v>0.1125935273763485</v>
       </c>
       <c r="O2">
-        <v>0.7000521405049397</v>
+        <v>1.332591361325913</v>
       </c>
       <c r="P2">
-        <v>25.5099</v>
+        <v>55.3172</v>
       </c>
       <c r="Q2">
-        <v>0.06284774575018479</v>
+        <v>0.1125935273763485</v>
       </c>
       <c r="R2">
-        <v>0.7000521405049397</v>
+        <v>1.332591361325913</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.011</v>
+        <v>176.25</v>
       </c>
       <c r="V2">
-        <v>0.01234540527223454</v>
+        <v>0.3587421127620598</v>
       </c>
       <c r="W2">
-        <v>0.07318295739348371</v>
+        <v>0.09836493850799027</v>
       </c>
       <c r="X2">
-        <v>0.07114010561210969</v>
+        <v>0.1133417007015411</v>
       </c>
       <c r="Y2">
-        <v>0.002042851781374019</v>
+        <v>-0.01497676219355082</v>
       </c>
       <c r="Z2">
-        <v>0.1253306623520045</v>
+        <v>0.157007890999479</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0509012511173884</v>
+        <v>0.08704111698914983</v>
       </c>
       <c r="AC2">
-        <v>-0.0509012511173884</v>
+        <v>-0.08704111698914983</v>
       </c>
       <c r="AD2">
-        <v>918.6999999999999</v>
+        <v>1151.605</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>918.6999999999999</v>
+        <v>1151.605</v>
       </c>
       <c r="AG2">
-        <v>913.689</v>
+        <v>975.355</v>
       </c>
       <c r="AH2">
-        <v>0.6935678695455232</v>
+        <v>0.7009565373530423</v>
       </c>
       <c r="AI2">
-        <v>0.6950370706612196</v>
+        <v>0.7667067239674704</v>
       </c>
       <c r="AJ2">
-        <v>0.6924042258612341</v>
+        <v>0.6650200626595894</v>
       </c>
       <c r="AK2">
-        <v>0.6938765436224027</v>
+        <v>0.7356922229806943</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.063</v>
+      </c>
+      <c r="AN2">
+        <v>967.7352941176471</v>
+      </c>
+      <c r="AO2">
+        <v>8.174603174603174</v>
+      </c>
+      <c r="AP2">
+        <v>819.6260504201681</v>
+      </c>
+      <c r="AQ2">
+        <v>8.174603174603174</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equita Group S.p.A. (BIT:EQUI)</t>
+          <t>Finanza.tech S.p.A. (BIT:FTC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,22 +722,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.2600877192982456</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.2587719298245614</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.1129385964912281</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1015411234508289</v>
       </c>
       <c r="K3">
-        <v>20.3</v>
+        <v>0.416</v>
       </c>
       <c r="L3">
-        <v>0.1986301369863014</v>
+        <v>0.0912280701754386</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,61 +761,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.001</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
-        <v>5.356186395286557e-06</v>
+        <v>0.16</v>
       </c>
       <c r="W3">
-        <v>0.2123430962343096</v>
+        <v>0.1133514986376022</v>
       </c>
       <c r="X3">
-        <v>0.06794988494856465</v>
+        <v>0.08421028194080481</v>
       </c>
       <c r="Y3">
-        <v>0.144393211285745</v>
+        <v>0.02914121669679737</v>
       </c>
       <c r="Z3">
-        <v>0.3459715639810427</v>
+        <v>1.154722714611294</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.1172518417158217</v>
       </c>
       <c r="AB3">
-        <v>0.04860558033129038</v>
+        <v>0.08360317155942247</v>
       </c>
       <c r="AC3">
-        <v>-0.04860558033129038</v>
+        <v>0.03364867015639923</v>
       </c>
       <c r="AD3">
-        <v>217.2</v>
+        <v>0.345</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>217.2</v>
+        <v>0.345</v>
       </c>
       <c r="AG3">
-        <v>217.199</v>
+        <v>-1.335</v>
       </c>
       <c r="AH3">
-        <v>0.5377568705125031</v>
+        <v>0.0318118948824343</v>
       </c>
       <c r="AI3">
-        <v>0.6730709637434149</v>
+        <v>0.04204753199268738</v>
       </c>
       <c r="AJ3">
-        <v>0.5377557260602279</v>
+        <v>-0.1456628477905074</v>
       </c>
       <c r="AK3">
-        <v>0.673069950635112</v>
+        <v>-0.2045977011494253</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.063</v>
+      </c>
+      <c r="AN3">
+        <v>0.2899159663865546</v>
+      </c>
+      <c r="AO3">
+        <v>8.174603174603174</v>
+      </c>
+      <c r="AP3">
+        <v>-1.121848739495798</v>
+      </c>
+      <c r="AQ3">
+        <v>8.174603174603174</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banca Intermobiliare di Investimenti e Gestioni SpA (BIT:BIM)</t>
+          <t>MiT Sim S.p.A. (BIT:MTS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -822,9 +846,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.00049</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -838,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1.54</v>
+        <v>-0.385</v>
       </c>
       <c r="L4">
-        <v>0.02308845577211394</v>
+        <v>-0.1420664206642067</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -850,7 +871,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -859,61 +880,61 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V4">
-        <v>0.02026359143327842</v>
+        <v>0.1207920792079208</v>
       </c>
       <c r="W4">
-        <v>0.01661272923408846</v>
+        <v>-0.1258169934640523</v>
       </c>
       <c r="X4">
-        <v>0.07114010561210969</v>
+        <v>0.08497085604308349</v>
       </c>
       <c r="Y4">
-        <v>-0.05452737637802123</v>
+        <v>-0.2107878495071358</v>
       </c>
       <c r="Z4">
-        <v>0.1745616330803454</v>
+        <v>0.8048708048708049</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0509012511173884</v>
+        <v>0.08346920727217465</v>
       </c>
       <c r="AC4">
-        <v>-0.0509012511173884</v>
+        <v>-0.08346920727217465</v>
       </c>
       <c r="AD4">
-        <v>79.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>79.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG4">
-        <v>78.47</v>
+        <v>-0.6599999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.5676638176638177</v>
+        <v>0.0525328330206379</v>
       </c>
       <c r="AI4">
-        <v>0.4549086757990868</v>
+        <v>0.1362530413625304</v>
       </c>
       <c r="AJ4">
-        <v>0.5638427822088093</v>
+        <v>-0.06991525423728813</v>
       </c>
       <c r="AK4">
-        <v>0.4510547795596942</v>
+        <v>-0.2283737024221453</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -930,117 +951,471 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Equita Group S.p.A. (BIT:EQUI)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.121</v>
+      </c>
+      <c r="E5">
+        <v>0.149</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>20.2</v>
+      </c>
+      <c r="L5">
+        <v>0.2063329928498468</v>
+      </c>
+      <c r="M5">
+        <v>16.0867</v>
+      </c>
+      <c r="N5">
+        <v>0.08824300603400988</v>
+      </c>
+      <c r="O5">
+        <v>0.796371287128713</v>
+      </c>
+      <c r="P5">
+        <v>16.0867</v>
+      </c>
+      <c r="Q5">
+        <v>0.08824300603400988</v>
+      </c>
+      <c r="R5">
+        <v>0.796371287128713</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>109.1</v>
+      </c>
+      <c r="V5">
+        <v>0.598464070213933</v>
+      </c>
+      <c r="W5">
+        <v>0.1914691943127962</v>
+      </c>
+      <c r="X5">
+        <v>0.1194161753174662</v>
+      </c>
+      <c r="Y5">
+        <v>0.07205301899533</v>
+      </c>
+      <c r="Z5">
+        <v>0.3322033668251335</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.08671162977040675</v>
+      </c>
+      <c r="AC5">
+        <v>-0.08671162977040675</v>
+      </c>
+      <c r="AD5">
+        <v>196.6</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>196.6</v>
+      </c>
+      <c r="AG5">
+        <v>87.5</v>
+      </c>
+      <c r="AH5">
+        <v>0.5188704143573503</v>
+      </c>
+      <c r="AI5">
+        <v>0.6700749829584186</v>
+      </c>
+      <c r="AJ5">
+        <v>0.3243143068939955</v>
+      </c>
+      <c r="AK5">
+        <v>0.4747693977211069</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Intermonte Partners SIM S.p.A. (BIT:INT)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>6.17</v>
+      </c>
+      <c r="L6">
+        <v>0.1408675799086758</v>
+      </c>
+      <c r="M6">
+        <v>26.8</v>
+      </c>
+      <c r="N6">
+        <v>0.3134502923976608</v>
+      </c>
+      <c r="O6">
+        <v>4.343598055105349</v>
+      </c>
+      <c r="P6">
+        <v>26.8</v>
+      </c>
+      <c r="Q6">
+        <v>0.3134502923976608</v>
+      </c>
+      <c r="R6">
+        <v>4.343598055105349</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>11.5</v>
+      </c>
+      <c r="V6">
+        <v>0.1345029239766082</v>
+      </c>
+      <c r="W6">
+        <v>0.08337837837837837</v>
+      </c>
+      <c r="X6">
+        <v>0.1365837381964194</v>
+      </c>
+      <c r="Y6">
+        <v>-0.05320535981804099</v>
+      </c>
+      <c r="Z6">
+        <v>0.1279627914586297</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.08737060420789292</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08737060420789292</v>
+      </c>
+      <c r="AD6">
+        <v>135.8</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>135.8</v>
+      </c>
+      <c r="AG6">
+        <v>124.3</v>
+      </c>
+      <c r="AH6">
+        <v>0.6136466335291459</v>
+      </c>
+      <c r="AI6">
+        <v>0.6872469635627531</v>
+      </c>
+      <c r="AJ6">
+        <v>0.5924690181124881</v>
+      </c>
+      <c r="AK6">
+        <v>0.6679204728640515</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Directa S.I.M.p.A. (BIT:D)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>5.3</v>
+      </c>
+      <c r="L7">
+        <v>0.1760797342192691</v>
+      </c>
+      <c r="M7">
+        <v>2.5905</v>
+      </c>
+      <c r="N7">
+        <v>0.04041341653666147</v>
+      </c>
+      <c r="O7">
+        <v>0.4887735849056604</v>
+      </c>
+      <c r="P7">
+        <v>2.5905</v>
+      </c>
+      <c r="Q7">
+        <v>0.04041341653666147</v>
+      </c>
+      <c r="R7">
+        <v>0.4887735849056604</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>6.45</v>
+      </c>
+      <c r="V7">
+        <v>0.1006240249609985</v>
+      </c>
+      <c r="W7">
+        <v>0.2145748987854251</v>
+      </c>
+      <c r="X7">
+        <v>0.107267226085616</v>
+      </c>
+      <c r="Y7">
+        <v>0.1073076726998091</v>
+      </c>
+      <c r="Z7">
+        <v>0.3960526315789474</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.08845388328688603</v>
+      </c>
+      <c r="AC7">
+        <v>-0.08845388328688603</v>
+      </c>
+      <c r="AD7">
+        <v>46</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>46</v>
+      </c>
+      <c r="AG7">
+        <v>39.55</v>
+      </c>
+      <c r="AH7">
+        <v>0.4178019981834696</v>
+      </c>
+      <c r="AI7">
+        <v>0.6108897742363878</v>
+      </c>
+      <c r="AJ7">
+        <v>0.3815726000964785</v>
+      </c>
+      <c r="AK7">
+        <v>0.5744371822803196</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Banca Profilo S.p.A. (BIT:PRO)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.0455</v>
-      </c>
-      <c r="E5">
-        <v>0.535</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>14.6</v>
-      </c>
-      <c r="L5">
-        <v>0.1944074567243675</v>
-      </c>
-      <c r="M5">
-        <v>25.5099</v>
-      </c>
-      <c r="N5">
-        <v>0.1609457413249211</v>
-      </c>
-      <c r="O5">
-        <v>1.747253424657534</v>
-      </c>
-      <c r="P5">
-        <v>25.5099</v>
-      </c>
-      <c r="Q5">
-        <v>0.1609457413249211</v>
-      </c>
-      <c r="R5">
-        <v>1.747253424657534</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>3.78</v>
-      </c>
-      <c r="V5">
-        <v>0.02384858044164038</v>
-      </c>
-      <c r="W5">
-        <v>0.07318295739348371</v>
-      </c>
-      <c r="X5">
-        <v>0.1267796356238627</v>
-      </c>
-      <c r="Y5">
-        <v>-0.05359667823037897</v>
-      </c>
-      <c r="Z5">
-        <v>0.0591641391263245</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.05123451076010918</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05123451076010918</v>
-      </c>
-      <c r="AD5">
-        <v>621.8</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>621.8</v>
-      </c>
-      <c r="AG5">
-        <v>618.02</v>
-      </c>
-      <c r="AH5">
-        <v>0.796872997565039</v>
-      </c>
-      <c r="AI5">
-        <v>0.7547032406845491</v>
-      </c>
-      <c r="AJ5">
-        <v>0.7958842013084015</v>
-      </c>
-      <c r="AK5">
-        <v>0.7535726479051846</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="D8">
+        <v>0.0208</v>
+      </c>
+      <c r="E8">
+        <v>0.163</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>9.81</v>
+      </c>
+      <c r="L8">
+        <v>0.1567092651757188</v>
+      </c>
+      <c r="M8">
+        <v>9.84</v>
+      </c>
+      <c r="N8">
+        <v>0.07089337175792507</v>
+      </c>
+      <c r="O8">
+        <v>1.003058103975535</v>
+      </c>
+      <c r="P8">
+        <v>9.84</v>
+      </c>
+      <c r="Q8">
+        <v>0.07089337175792507</v>
+      </c>
+      <c r="R8">
+        <v>1.003058103975535</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>46.3</v>
+      </c>
+      <c r="V8">
+        <v>0.3335734870317003</v>
+      </c>
+      <c r="W8">
+        <v>0.04854032657100445</v>
+      </c>
+      <c r="X8">
+        <v>0.2704534755709047</v>
+      </c>
+      <c r="Y8">
+        <v>-0.2219131489999003</v>
+      </c>
+      <c r="Z8">
+        <v>0.0764421433107019</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.08899766465888428</v>
+      </c>
+      <c r="AC8">
+        <v>-0.08899766465888428</v>
+      </c>
+      <c r="AD8">
+        <v>772.3</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>772.3</v>
+      </c>
+      <c r="AG8">
+        <v>726</v>
+      </c>
+      <c r="AH8">
+        <v>0.8476566787399846</v>
+      </c>
+      <c r="AI8">
+        <v>0.8363656053714533</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8395004625346901</v>
+      </c>
+      <c r="AK8">
+        <v>0.8277277391403488</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/italy/italy_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_brokerage_investment_banking.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07089999999999999</v>
+        <v>0.0519</v>
       </c>
       <c r="E2">
-        <v>0.156</v>
+        <v>0.12245</v>
       </c>
       <c r="G2">
-        <v>0.004907518516985972</v>
+        <v>0.004053417124901807</v>
       </c>
       <c r="H2">
-        <v>0.004882691273223817</v>
+        <v>0.004045561665357423</v>
       </c>
       <c r="I2">
-        <v>0.002131005089584971</v>
+        <v>0.00375490966221524</v>
       </c>
       <c r="J2">
-        <v>0.001722946570393526</v>
+        <v>0.002882990927185962</v>
       </c>
       <c r="K2">
-        <v>41.511</v>
+        <v>36.78</v>
       </c>
       <c r="L2">
-        <v>0.1717672859684694</v>
+        <v>0.1444619010212098</v>
       </c>
       <c r="M2">
-        <v>55.3172</v>
+        <v>31.992</v>
       </c>
       <c r="N2">
-        <v>0.1125935273763485</v>
+        <v>0.06163211836325807</v>
       </c>
       <c r="O2">
-        <v>1.332591361325913</v>
+        <v>0.8698205546492659</v>
       </c>
       <c r="P2">
-        <v>55.3172</v>
+        <v>31.865</v>
       </c>
       <c r="Q2">
-        <v>0.1125935273763485</v>
+        <v>0.06138745472759496</v>
       </c>
       <c r="R2">
-        <v>1.332591361325913</v>
+        <v>0.8663675910821098</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.127000000000001</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.003969742435608934</v>
       </c>
       <c r="U2">
-        <v>176.25</v>
+        <v>129.209</v>
       </c>
       <c r="V2">
-        <v>0.3587421127620598</v>
+        <v>0.248919241735378</v>
       </c>
       <c r="W2">
-        <v>0.09836493850799027</v>
+        <v>0.08673417836628086</v>
       </c>
       <c r="X2">
-        <v>0.1133417007015411</v>
+        <v>0.09253166560636272</v>
       </c>
       <c r="Y2">
-        <v>-0.01497676219355082</v>
+        <v>-0.005797487240081861</v>
       </c>
       <c r="Z2">
-        <v>0.157007890999479</v>
+        <v>0.1653188784289382</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08704111698914983</v>
+        <v>0.07226276721216182</v>
       </c>
       <c r="AC2">
-        <v>-0.08704111698914983</v>
+        <v>-0.07226276721216182</v>
       </c>
       <c r="AD2">
-        <v>1151.605</v>
+        <v>1539.747</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1151.605</v>
+        <v>1539.747</v>
       </c>
       <c r="AG2">
-        <v>975.355</v>
+        <v>1410.538</v>
       </c>
       <c r="AH2">
-        <v>0.7009565373530423</v>
+        <v>0.747875853580704</v>
       </c>
       <c r="AI2">
-        <v>0.7667067239674704</v>
+        <v>0.8036689863807918</v>
       </c>
       <c r="AJ2">
-        <v>0.6650200626595894</v>
+        <v>0.7309933883286743</v>
       </c>
       <c r="AK2">
-        <v>0.7356922229806943</v>
+        <v>0.7894707973636136</v>
       </c>
       <c r="AL2">
-        <v>0.063</v>
+        <v>0.031</v>
       </c>
       <c r="AM2">
-        <v>0.063</v>
+        <v>0.031</v>
       </c>
       <c r="AN2">
-        <v>967.7352941176471</v>
+        <v>827.8209677419353</v>
       </c>
       <c r="AO2">
-        <v>8.174603174603174</v>
+        <v>30.83870967741935</v>
       </c>
       <c r="AP2">
-        <v>819.6260504201681</v>
+        <v>758.35376344086</v>
       </c>
       <c r="AQ2">
-        <v>8.174603174603174</v>
+        <v>30.83870967741935</v>
       </c>
     </row>
     <row r="3">
@@ -722,31 +722,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.2600877192982456</v>
+        <v>0.1001941747572816</v>
       </c>
       <c r="H3">
-        <v>0.2587719298245614</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="I3">
-        <v>0.1129385964912281</v>
+        <v>0.09281553398058251</v>
       </c>
       <c r="J3">
-        <v>0.1015411234508289</v>
+        <v>0.06791380535164573</v>
       </c>
       <c r="K3">
-        <v>0.416</v>
+        <v>0.63</v>
       </c>
       <c r="L3">
-        <v>0.0912280701754386</v>
+        <v>0.06116504854368932</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.007</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0006542056074766356</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,76 +758,79 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.007</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>0.931</v>
       </c>
       <c r="V3">
-        <v>0.16</v>
+        <v>0.08700934579439254</v>
       </c>
       <c r="W3">
-        <v>0.1133514986376022</v>
+        <v>0.08015267175572519</v>
       </c>
       <c r="X3">
-        <v>0.08421028194080481</v>
+        <v>0.07084019159681974</v>
       </c>
       <c r="Y3">
-        <v>0.02914121669679737</v>
+        <v>0.009312480158905442</v>
       </c>
       <c r="Z3">
-        <v>1.154722714611294</v>
+        <v>2.099898063200816</v>
       </c>
       <c r="AA3">
-        <v>0.1172518417158217</v>
+        <v>0.1426120683225181</v>
       </c>
       <c r="AB3">
-        <v>0.08360317155942247</v>
+        <v>0.06983066055553712</v>
       </c>
       <c r="AC3">
-        <v>0.03364867015639923</v>
+        <v>0.07278140776698096</v>
       </c>
       <c r="AD3">
-        <v>0.345</v>
+        <v>0.832</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.345</v>
+        <v>0.832</v>
       </c>
       <c r="AG3">
-        <v>-1.335</v>
+        <v>-0.09900000000000009</v>
       </c>
       <c r="AH3">
-        <v>0.0318118948824343</v>
+        <v>0.07214706902532084</v>
       </c>
       <c r="AI3">
-        <v>0.04204753199268738</v>
+        <v>0.08602150537634408</v>
       </c>
       <c r="AJ3">
-        <v>-0.1456628477905074</v>
+        <v>-0.009338741628148297</v>
       </c>
       <c r="AK3">
-        <v>-0.2045977011494253</v>
+        <v>-0.01132593524768334</v>
       </c>
       <c r="AL3">
-        <v>0.063</v>
+        <v>0.031</v>
       </c>
       <c r="AM3">
-        <v>0.063</v>
+        <v>0.031</v>
       </c>
       <c r="AN3">
-        <v>0.2899159663865546</v>
+        <v>0.4473118279569892</v>
       </c>
       <c r="AO3">
-        <v>8.174603174603174</v>
+        <v>30.83870967741935</v>
       </c>
       <c r="AP3">
-        <v>-1.121848739495798</v>
+        <v>-0.05322580645161295</v>
       </c>
       <c r="AQ3">
-        <v>8.174603174603174</v>
+        <v>30.83870967741935</v>
       </c>
     </row>
     <row r="4">
@@ -859,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-0.385</v>
+        <v>-0.4</v>
       </c>
       <c r="L4">
-        <v>-0.1420664206642067</v>
+        <v>-0.1379310344827586</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.22</v>
+        <v>0.298</v>
       </c>
       <c r="V4">
-        <v>0.1207920792079208</v>
+        <v>0.03599033816425121</v>
       </c>
       <c r="W4">
-        <v>-0.1258169934640523</v>
+        <v>-0.1126760563380282</v>
       </c>
       <c r="X4">
-        <v>0.08497085604308349</v>
+        <v>0.07020478379376494</v>
       </c>
       <c r="Y4">
-        <v>-0.2107878495071358</v>
+        <v>-0.1828808401317931</v>
       </c>
       <c r="Z4">
-        <v>0.8048708048708049</v>
+        <v>1.003460207612457</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08346920727217465</v>
+        <v>0.06935643717351031</v>
       </c>
       <c r="AC4">
-        <v>-0.08346920727217465</v>
+        <v>-0.06935643717351031</v>
       </c>
       <c r="AD4">
-        <v>0.5600000000000001</v>
+        <v>0.415</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.5600000000000001</v>
+        <v>0.415</v>
       </c>
       <c r="AG4">
-        <v>-0.6599999999999999</v>
+        <v>0.117</v>
       </c>
       <c r="AH4">
-        <v>0.0525328330206379</v>
+        <v>0.04772857964347327</v>
       </c>
       <c r="AI4">
-        <v>0.1362530413625304</v>
+        <v>0.1114093959731544</v>
       </c>
       <c r="AJ4">
-        <v>-0.06991525423728813</v>
+        <v>0.01393354769560558</v>
       </c>
       <c r="AK4">
-        <v>-0.2283737024221453</v>
+        <v>0.03414064779690691</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equita Group S.p.A. (BIT:EQUI)</t>
+          <t>Directa S.I.M.p.A. (BIT:D)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -959,12 +962,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.121</v>
-      </c>
-      <c r="E5">
-        <v>0.149</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -978,28 +975,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>20.2</v>
+        <v>6.13</v>
       </c>
       <c r="L5">
-        <v>0.2063329928498468</v>
+        <v>0.186890243902439</v>
       </c>
       <c r="M5">
-        <v>16.0867</v>
+        <v>3.08</v>
       </c>
       <c r="N5">
-        <v>0.08824300603400988</v>
+        <v>0.04576523031203567</v>
       </c>
       <c r="O5">
-        <v>0.796371287128713</v>
+        <v>0.5024469820554649</v>
       </c>
       <c r="P5">
-        <v>16.0867</v>
+        <v>3.08</v>
       </c>
       <c r="Q5">
-        <v>0.08824300603400988</v>
+        <v>0.04576523031203567</v>
       </c>
       <c r="R5">
-        <v>0.796371287128713</v>
+        <v>0.5024469820554649</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1005,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>109.1</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="V5">
-        <v>0.598464070213933</v>
+        <v>0.1453194650817236</v>
       </c>
       <c r="W5">
-        <v>0.1914691943127962</v>
+        <v>0.2092150170648464</v>
       </c>
       <c r="X5">
-        <v>0.1194161753174662</v>
+        <v>0.09019943783536252</v>
       </c>
       <c r="Y5">
-        <v>0.07205301899533</v>
+        <v>0.1190155792294839</v>
       </c>
       <c r="Z5">
-        <v>0.3322033668251335</v>
+        <v>0.476397966594045</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08671162977040675</v>
+        <v>0.07210420465854997</v>
       </c>
       <c r="AC5">
-        <v>-0.08671162977040675</v>
+        <v>-0.07210420465854997</v>
       </c>
       <c r="AD5">
-        <v>196.6</v>
+        <v>61.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>196.6</v>
+        <v>61.9</v>
       </c>
       <c r="AG5">
-        <v>87.5</v>
+        <v>52.12</v>
       </c>
       <c r="AH5">
-        <v>0.5188704143573503</v>
+        <v>0.4791021671826626</v>
       </c>
       <c r="AI5">
-        <v>0.6700749829584186</v>
+        <v>0.6401240951396071</v>
       </c>
       <c r="AJ5">
-        <v>0.3243143068939955</v>
+        <v>0.4364428069000167</v>
       </c>
       <c r="AK5">
-        <v>0.4747693977211069</v>
+        <v>0.5996318453750575</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intermonte Partners SIM S.p.A. (BIT:INT)</t>
+          <t>Equita Group S.p.A. (BIT:EQUI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,6 +1078,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.0516</v>
+      </c>
+      <c r="E6">
+        <v>-0.0221</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1094,85 +1097,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>6.17</v>
+        <v>12.6</v>
       </c>
       <c r="L6">
-        <v>0.1408675799086758</v>
+        <v>0.1340425531914894</v>
       </c>
       <c r="M6">
-        <v>26.8</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.3134502923976608</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>4.343598055105349</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>26.8</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.3134502923976608</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>4.343598055105349</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.1345029239766082</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.08337837837837837</v>
+        <v>0.1301652892561984</v>
       </c>
       <c r="X6">
-        <v>0.1365837381964194</v>
+        <v>0.09486389337736291</v>
       </c>
       <c r="Y6">
-        <v>-0.05320535981804099</v>
+        <v>0.03530139587883545</v>
       </c>
       <c r="Z6">
-        <v>0.1279627914586297</v>
+        <v>0.5853051058530511</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08737060420789292</v>
+        <v>0.07242132976577367</v>
       </c>
       <c r="AC6">
-        <v>-0.08737060420789292</v>
+        <v>-0.07242132976577367</v>
       </c>
       <c r="AD6">
-        <v>135.8</v>
+        <v>219.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>135.8</v>
+        <v>219.7</v>
       </c>
       <c r="AG6">
-        <v>124.3</v>
+        <v>219.7</v>
       </c>
       <c r="AH6">
-        <v>0.6136466335291459</v>
+        <v>0.5288878189696677</v>
       </c>
       <c r="AI6">
-        <v>0.6872469635627531</v>
+        <v>0.6867771178493279</v>
       </c>
       <c r="AJ6">
-        <v>0.5924690181124881</v>
+        <v>0.5288878189696677</v>
       </c>
       <c r="AK6">
-        <v>0.6679204728640515</v>
+        <v>0.6867771178493279</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Directa S.I.M.p.A. (BIT:D)</t>
+          <t>Intermonte Partners SIM S.p.A. (BIT:INT)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,85 +1210,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5.3</v>
+        <v>3.72</v>
       </c>
       <c r="L7">
-        <v>0.1760797342192691</v>
+        <v>0.1008130081300813</v>
       </c>
       <c r="M7">
-        <v>2.5905</v>
+        <v>19.02</v>
       </c>
       <c r="N7">
-        <v>0.04041341653666147</v>
+        <v>0.2132286995515695</v>
       </c>
       <c r="O7">
-        <v>0.4887735849056604</v>
+        <v>5.112903225806451</v>
       </c>
       <c r="P7">
-        <v>2.5905</v>
+        <v>18.9</v>
       </c>
       <c r="Q7">
-        <v>0.04041341653666147</v>
+        <v>0.2118834080717489</v>
       </c>
       <c r="R7">
-        <v>0.4887735849056604</v>
+        <v>5.080645161290322</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.120000000000001</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.00630914826498428</v>
       </c>
       <c r="U7">
-        <v>6.45</v>
+        <v>16.3</v>
       </c>
       <c r="V7">
-        <v>0.1006240249609985</v>
+        <v>0.1827354260089686</v>
       </c>
       <c r="W7">
-        <v>0.2145748987854251</v>
+        <v>0.07209302325581396</v>
       </c>
       <c r="X7">
-        <v>0.107267226085616</v>
+        <v>0.1147010035579177</v>
       </c>
       <c r="Y7">
-        <v>0.1073076726998091</v>
+        <v>-0.04260798030210376</v>
       </c>
       <c r="Z7">
-        <v>0.3960526315789474</v>
+        <v>0.2097782831154065</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.08845388328688603</v>
+        <v>0.07328858955746038</v>
       </c>
       <c r="AC7">
-        <v>-0.08845388328688603</v>
+        <v>-0.07328858955746038</v>
       </c>
       <c r="AD7">
-        <v>46</v>
+        <v>177.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>46</v>
+        <v>177.1</v>
       </c>
       <c r="AG7">
-        <v>39.55</v>
+        <v>160.8</v>
       </c>
       <c r="AH7">
-        <v>0.4178019981834696</v>
+        <v>0.6650394292151708</v>
       </c>
       <c r="AI7">
-        <v>0.6108897742363878</v>
+        <v>0.7504237288135593</v>
       </c>
       <c r="AJ7">
-        <v>0.3815726000964785</v>
+        <v>0.6431999999999999</v>
       </c>
       <c r="AK7">
-        <v>0.5744371822803196</v>
+        <v>0.7319071461083295</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0208</v>
+        <v>0.0522</v>
       </c>
       <c r="E8">
-        <v>0.163</v>
+        <v>0.267</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1332,28 +1332,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>9.81</v>
+        <v>14.1</v>
       </c>
       <c r="L8">
-        <v>0.1567092651757188</v>
+        <v>0.1814671814671815</v>
       </c>
       <c r="M8">
-        <v>9.84</v>
+        <v>9.885</v>
       </c>
       <c r="N8">
-        <v>0.07089337175792507</v>
+        <v>0.06683569979716024</v>
       </c>
       <c r="O8">
-        <v>1.003058103975535</v>
+        <v>0.701063829787234</v>
       </c>
       <c r="P8">
-        <v>9.84</v>
+        <v>9.885</v>
       </c>
       <c r="Q8">
-        <v>0.07089337175792507</v>
+        <v>0.06683569979716024</v>
       </c>
       <c r="R8">
-        <v>1.003058103975535</v>
+        <v>0.701063829787234</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1362,55 +1362,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>46.3</v>
+        <v>101.9</v>
       </c>
       <c r="V8">
-        <v>0.3335734870317003</v>
+        <v>0.6889790398918189</v>
       </c>
       <c r="W8">
-        <v>0.04854032657100445</v>
+        <v>0.09331568497683654</v>
       </c>
       <c r="X8">
-        <v>0.2704534755709047</v>
+        <v>0.2369130240698071</v>
       </c>
       <c r="Y8">
-        <v>-0.2219131489999003</v>
+        <v>-0.1435973390929706</v>
       </c>
       <c r="Z8">
-        <v>0.0764421433107019</v>
+        <v>0.06894966674327742</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.08899766465888428</v>
+        <v>0.07465485887468827</v>
       </c>
       <c r="AC8">
-        <v>-0.08899766465888428</v>
+        <v>-0.07465485887468827</v>
       </c>
       <c r="AD8">
-        <v>772.3</v>
+        <v>1079.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>772.3</v>
+        <v>1079.8</v>
       </c>
       <c r="AG8">
-        <v>726</v>
+        <v>977.9</v>
       </c>
       <c r="AH8">
-        <v>0.8476566787399846</v>
+        <v>0.8795308300073307</v>
       </c>
       <c r="AI8">
-        <v>0.8363656053714533</v>
+        <v>0.8639091127290184</v>
       </c>
       <c r="AJ8">
-        <v>0.8395004625346901</v>
+        <v>0.8686267543080476</v>
       </c>
       <c r="AK8">
-        <v>0.8277277391403488</v>
+        <v>0.8518292682926829</v>
       </c>
       <c r="AL8">
         <v>0</v>
